--- a/STM32H743VIT6引脚定义.xlsx
+++ b/STM32H743VIT6引脚定义.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MCU_Project\STM32H743Project\02High_Speed_Collection_AD7616\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CECC7B6-35C5-4296-B928-A81085F612AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D3CC0E-2F1F-489E-AFD4-2763D541150C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D862D2F7-4BB5-4946-9DE3-EE852D9A2767}"/>
   </bookViews>
@@ -1299,7 +1299,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">  </t>
+    <t xml:space="preserve">TIM2_CH3,HRTIM_SCOUT,LPTIM2_IN1, I2C2_SCL,SPI2_SCK/I2S2_CK,DFSDM1_DATIN7,USART3_TX,QUADSPI_BK1_NCS,OTG_HS_ULPI_D3,ETH_MII_RX_ER,LCD_G4, EVENTOUT  </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3027,7 +3027,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A48" s="7">
         <v>46</v>
       </c>

--- a/STM32H743VIT6引脚定义.xlsx
+++ b/STM32H743VIT6引脚定义.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MCU_Project\STM32H743Project\02High_Speed_Collection_AD7616\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D3CC0E-2F1F-489E-AFD4-2763D541150C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B2C65A-8F40-459A-8B8E-C073A17B4C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D862D2F7-4BB5-4946-9DE3-EE852D9A2767}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="272">
   <si>
     <t>I/O</t>
   </si>
@@ -434,10 +434,6 @@
   </si>
   <si>
     <t>VCAP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PB12</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1283,24 +1279,64 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>W25Q128_CS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>W25Q128_CLK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>W25Q128_DO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>W25Q128_DI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">TIM2_CH3,HRTIM_SCOUT,LPTIM2_IN1, I2C2_SCL,SPI2_SCK/I2S2_CK,DFSDM1_DATIN7,USART3_TX,QUADSPI_BK1_NCS,OTG_HS_ULPI_D3,ETH_MII_RX_ER,LCD_G4, EVENTOUT  </t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB_OTG_HS_ULPI_CK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB_OTG_HS_ULPI_D0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB_OTG_HS_ULPI_D1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB_OTG_HS_ULPI_D2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB_OTG_HS_ULPI_D3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB_OTG_HS_ULPI_D4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB_OTG_HS_ULPI_D5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB_OTG_HS_ULPI_D6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB_OTG_HS_ULPI_D7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CDSLEEP,DFSDM1_CKIN1,SPI2_MISO/I2S2_SDI,DFSDM1_CKOUT,OTG_HS_ULPI_DIR,ETH_MII_TXD2,FMC_SDNE0,EVENTOUT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CSLEEP,DFSDM1_DATIN1,SPI2_MOSI/I2S2_SDO,OTG_HS_ULPI_NXT,ETH_MII_TX_CLK,FMC_SDCKE0,EVENTOUT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB_OTG_HS_ULPI_DIR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB_OTG_HS_ULPI_NXT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB_OTG_HS_ULPI_STP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1893,7 +1929,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1905,28 +1941,28 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>208</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.2">
@@ -2057,19 +2093,19 @@
         <v>4</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H8" s="14"/>
     </row>
@@ -2096,7 +2132,7 @@
         <v>28</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
@@ -2104,22 +2140,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C10" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="E10" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="F10" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="E10" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F10" s="16" t="s">
+      <c r="G10" s="17" t="s">
         <v>214</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>215</v>
       </c>
       <c r="H10" s="17"/>
     </row>
@@ -2128,22 +2164,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C11" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="D11" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="E11" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="F11" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="E11" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>214</v>
-      </c>
       <c r="G11" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H11" s="17"/>
     </row>
@@ -2155,19 +2191,19 @@
         <v>5</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H12" s="14"/>
     </row>
@@ -2179,19 +2215,19 @@
         <v>6</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H13" s="14"/>
     </row>
@@ -2200,22 +2236,22 @@
         <v>12</v>
       </c>
       <c r="B14" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="G14" s="17" t="s">
         <v>217</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>218</v>
       </c>
       <c r="H14" s="17"/>
     </row>
@@ -2224,22 +2260,22 @@
         <v>13</v>
       </c>
       <c r="B15" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="G15" s="17" t="s">
         <v>219</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>220</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -2248,22 +2284,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="D16" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="C16" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>222</v>
-      </c>
       <c r="E16" s="15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -2289,7 +2325,9 @@
       <c r="G17" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H17" s="10"/>
+      <c r="H17" s="10" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
@@ -2315,7 +2353,7 @@
       </c>
       <c r="H18" s="10"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>17</v>
       </c>
@@ -2331,13 +2369,17 @@
       <c r="E19" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F19" s="9"/>
+      <c r="F19" s="9" t="s">
+        <v>267</v>
+      </c>
       <c r="G19" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="H19" s="10"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H19" s="10" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>18</v>
       </c>
@@ -2353,11 +2395,15 @@
       <c r="E20" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F20" s="9"/>
+      <c r="F20" s="9" t="s">
+        <v>268</v>
+      </c>
       <c r="G20" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="H20" s="10"/>
+      <c r="H20" s="10" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="11">
@@ -2367,19 +2413,19 @@
         <v>7</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H21" s="14"/>
     </row>
@@ -2391,19 +2437,19 @@
         <v>8</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H22" s="14"/>
     </row>
@@ -2415,19 +2461,19 @@
         <v>9</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H23" s="14"/>
     </row>
@@ -2454,7 +2500,7 @@
         <v>45</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="75" x14ac:dyDescent="0.2">
@@ -2527,7 +2573,9 @@
       <c r="G27" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H27" s="10"/>
+      <c r="H27" s="10" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="11">
@@ -2537,19 +2585,19 @@
         <v>5</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H28" s="14"/>
     </row>
@@ -2561,19 +2609,19 @@
         <v>6</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H29" s="14"/>
     </row>
@@ -2623,7 +2671,9 @@
       <c r="G31" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="H31" s="10"/>
+      <c r="H31" s="10" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="32" spans="1:8" ht="75" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
@@ -2743,7 +2793,9 @@
       <c r="G36" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="H36" s="10"/>
+      <c r="H36" s="10" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="37" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A37" s="7">
@@ -2767,7 +2819,9 @@
       <c r="G37" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="H37" s="10"/>
+      <c r="H37" s="10" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="38" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
@@ -2816,7 +2870,7 @@
         <v>86</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="45" x14ac:dyDescent="0.2">
@@ -2842,7 +2896,7 @@
         <v>89</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="30" x14ac:dyDescent="0.2">
@@ -2868,7 +2922,7 @@
         <v>92</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="30" x14ac:dyDescent="0.2">
@@ -2894,7 +2948,7 @@
         <v>95</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="30" x14ac:dyDescent="0.2">
@@ -2920,7 +2974,7 @@
         <v>97</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="45" x14ac:dyDescent="0.2">
@@ -2946,7 +3000,7 @@
         <v>2</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="45" x14ac:dyDescent="0.2">
@@ -2972,7 +3026,7 @@
         <v>2</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="30" x14ac:dyDescent="0.2">
@@ -2998,7 +3052,7 @@
         <v>2</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="45" x14ac:dyDescent="0.2">
@@ -3024,7 +3078,7 @@
         <v>2</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="60" x14ac:dyDescent="0.2">
@@ -3044,12 +3098,14 @@
         <v>2</v>
       </c>
       <c r="F48" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="H48" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="G48" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="H48" s="10"/>
     </row>
     <row r="49" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A49" s="7">
@@ -3073,7 +3129,9 @@
       <c r="G49" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="H49" s="10"/>
+      <c r="H49" s="10" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="11">
@@ -3083,19 +3141,19 @@
         <v>110</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H50" s="14"/>
     </row>
@@ -3107,19 +3165,19 @@
         <v>5</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H51" s="14"/>
     </row>
@@ -3131,19 +3189,19 @@
         <v>6</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H52" s="14"/>
     </row>
@@ -3151,24 +3209,24 @@
       <c r="A53" s="7">
         <v>51</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="8">
+        <v>5</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D53" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="C53" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D53" s="8" t="s">
+      <c r="E53" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F53" s="9" t="s">
         <v>112</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>113</v>
       </c>
       <c r="G53" s="10"/>
       <c r="H53" s="10" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="75" x14ac:dyDescent="0.2">
@@ -3176,25 +3234,25 @@
         <v>52</v>
       </c>
       <c r="B54" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F54" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F54" s="9" t="s">
+      <c r="G54" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="G54" s="10" t="s">
-        <v>116</v>
-      </c>
       <c r="H54" s="10" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="60" x14ac:dyDescent="0.2">
@@ -3202,59 +3260,55 @@
         <v>53</v>
       </c>
       <c r="B55" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F55" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="C55" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>118</v>
-      </c>
       <c r="G55" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="H55" s="10" t="s">
-        <v>260</v>
-      </c>
+      <c r="H55" s="10"/>
     </row>
     <row r="56" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A56" s="7">
         <v>54</v>
       </c>
       <c r="B56" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F56" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="C56" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>120</v>
-      </c>
       <c r="G56" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="H56" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="H56" s="10"/>
     </row>
     <row r="57" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A57" s="7">
         <v>55</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>0</v>
@@ -3266,13 +3320,13 @@
         <v>2</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G57" s="10" t="s">
         <v>2</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="45" x14ac:dyDescent="0.2">
@@ -3280,7 +3334,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>0</v>
@@ -3292,13 +3346,13 @@
         <v>2</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G58" s="10" t="s">
         <v>2</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="45" x14ac:dyDescent="0.2">
@@ -3306,7 +3360,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>0</v>
@@ -3318,13 +3372,13 @@
         <v>2</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G59" s="10" t="s">
         <v>2</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="45" x14ac:dyDescent="0.2">
@@ -3332,7 +3386,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>0</v>
@@ -3344,7 +3398,7 @@
         <v>2</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G60" s="10" t="s">
         <v>2</v>
@@ -3356,19 +3410,19 @@
         <v>59</v>
       </c>
       <c r="B61" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D61" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C61" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D61" s="8" t="s">
+      <c r="E61" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F61" s="9" t="s">
         <v>130</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>131</v>
       </c>
       <c r="G61" s="10" t="s">
         <v>2</v>
@@ -3380,19 +3434,19 @@
         <v>60</v>
       </c>
       <c r="B62" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F62" s="9" t="s">
         <v>132</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>133</v>
       </c>
       <c r="G62" s="10" t="s">
         <v>2</v>
@@ -3404,7 +3458,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>0</v>
@@ -3416,13 +3470,13 @@
         <v>2</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G63" s="10" t="s">
         <v>2</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="30" x14ac:dyDescent="0.2">
@@ -3430,7 +3484,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>0</v>
@@ -3442,13 +3496,13 @@
         <v>2</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G64" s="10" t="s">
         <v>2</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="60" x14ac:dyDescent="0.2">
@@ -3456,7 +3510,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>0</v>
@@ -3468,10 +3522,10 @@
         <v>2</v>
       </c>
       <c r="F65" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G65" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="G65" s="10" t="s">
-        <v>140</v>
       </c>
       <c r="H65" s="10"/>
     </row>
@@ -3480,7 +3534,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>0</v>
@@ -3492,13 +3546,13 @@
         <v>2</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G66" s="10" t="s">
         <v>2</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="60" x14ac:dyDescent="0.2">
@@ -3506,7 +3560,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>0</v>
@@ -3518,7 +3572,7 @@
         <v>2</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G67" s="10" t="s">
         <v>2</v>
@@ -3530,19 +3584,19 @@
         <v>66</v>
       </c>
       <c r="B68" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F68" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="G68" s="10" t="s">
         <v>2</v>
@@ -3560,13 +3614,13 @@
         <v>0</v>
       </c>
       <c r="D69" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F69" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>148</v>
       </c>
       <c r="G69" s="10" t="s">
         <v>2</v>
@@ -3578,25 +3632,25 @@
         <v>68</v>
       </c>
       <c r="B70" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F70" s="9" t="s">
         <v>149</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F70" s="9" t="s">
-        <v>150</v>
       </c>
       <c r="G70" s="10" t="s">
         <v>3</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="45" x14ac:dyDescent="0.2">
@@ -3604,25 +3658,25 @@
         <v>69</v>
       </c>
       <c r="B71" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F71" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="C71" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>152</v>
-      </c>
       <c r="G71" s="10" t="s">
         <v>2</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="60" x14ac:dyDescent="0.2">
@@ -3630,25 +3684,25 @@
         <v>70</v>
       </c>
       <c r="B72" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F72" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="C72" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F72" s="9" t="s">
-        <v>154</v>
-      </c>
       <c r="G72" s="10" t="s">
         <v>2</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="60" x14ac:dyDescent="0.2">
@@ -3656,25 +3710,25 @@
         <v>71</v>
       </c>
       <c r="B73" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F73" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="C73" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>156</v>
-      </c>
       <c r="G73" s="10" t="s">
         <v>2</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
@@ -3682,22 +3736,22 @@
         <v>72</v>
       </c>
       <c r="B74" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="D74" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="E74" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="F74" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="C74" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="D74" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="E74" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F74" s="16" t="s">
-        <v>224</v>
-      </c>
       <c r="G74" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H74" s="17"/>
     </row>
@@ -3709,19 +3763,19 @@
         <v>110</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G75" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H75" s="14"/>
     </row>
@@ -3733,19 +3787,19 @@
         <v>5</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F76" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G76" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H76" s="14"/>
     </row>
@@ -3757,19 +3811,19 @@
         <v>6</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F77" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G77" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H77" s="14"/>
     </row>
@@ -3778,22 +3832,22 @@
         <v>76</v>
       </c>
       <c r="B78" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="D78" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="E78" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="F78" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="C78" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="D78" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="E78" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F78" s="16" t="s">
-        <v>226</v>
-      </c>
       <c r="G78" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H78" s="17"/>
     </row>
@@ -3802,7 +3856,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>0</v>
@@ -3814,7 +3868,7 @@
         <v>2</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G79" s="10" t="s">
         <v>2</v>
@@ -3826,7 +3880,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>0</v>
@@ -3838,7 +3892,7 @@
         <v>2</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G80" s="10" t="s">
         <v>2</v>
@@ -3850,7 +3904,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>0</v>
@@ -3862,7 +3916,7 @@
         <v>2</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G81" s="10" t="s">
         <v>2</v>
@@ -3874,7 +3928,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>0</v>
@@ -3886,7 +3940,7 @@
         <v>2</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G82" s="10" t="s">
         <v>2</v>
@@ -3898,7 +3952,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>0</v>
@@ -3910,13 +3964,13 @@
         <v>2</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G83" s="10" t="s">
         <v>2</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="30" x14ac:dyDescent="0.2">
@@ -3924,7 +3978,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>0</v>
@@ -3936,13 +3990,13 @@
         <v>2</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G84" s="10" t="s">
         <v>2</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="30" x14ac:dyDescent="0.2">
@@ -3950,7 +4004,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>0</v>
@@ -3962,7 +4016,7 @@
         <v>2</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G85" s="10" t="s">
         <v>2</v>
@@ -3974,7 +4028,7 @@
         <v>84</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>0</v>
@@ -3986,7 +4040,7 @@
         <v>2</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G86" s="10" t="s">
         <v>2</v>
@@ -3998,7 +4052,7 @@
         <v>85</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>0</v>
@@ -4010,13 +4064,13 @@
         <v>2</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G87" s="10" t="s">
         <v>2</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="30" x14ac:dyDescent="0.2">
@@ -4024,7 +4078,7 @@
         <v>86</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>0</v>
@@ -4036,13 +4090,13 @@
         <v>2</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G88" s="10" t="s">
         <v>2</v>
       </c>
       <c r="H88" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="75" x14ac:dyDescent="0.2">
@@ -4050,7 +4104,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>0</v>
@@ -4062,7 +4116,7 @@
         <v>2</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G89" s="10" t="s">
         <v>2</v>
@@ -4074,7 +4128,7 @@
         <v>88</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>0</v>
@@ -4086,7 +4140,7 @@
         <v>2</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G90" s="10" t="s">
         <v>2</v>
@@ -4098,7 +4152,7 @@
         <v>89</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>0</v>
@@ -4110,7 +4164,7 @@
         <v>2</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G91" s="10" t="s">
         <v>2</v>
@@ -4122,7 +4176,7 @@
         <v>90</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>0</v>
@@ -4134,7 +4188,7 @@
         <v>2</v>
       </c>
       <c r="F92" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G92" s="10" t="s">
         <v>2</v>
@@ -4146,7 +4200,7 @@
         <v>91</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>0</v>
@@ -4158,19 +4212,21 @@
         <v>2</v>
       </c>
       <c r="F93" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G93" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="H93" s="10"/>
+      <c r="H93" s="10" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="94" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A94" s="7">
         <v>92</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>0</v>
@@ -4182,7 +4238,7 @@
         <v>2</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G94" s="10" t="s">
         <v>2</v>
@@ -4194,22 +4250,22 @@
         <v>93</v>
       </c>
       <c r="B95" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D95" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="C95" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D95" s="8" t="s">
+      <c r="E95" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F95" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="E95" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F95" s="9" t="s">
+      <c r="G95" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="G95" s="10" t="s">
-        <v>192</v>
       </c>
       <c r="H95" s="10"/>
     </row>
@@ -4218,22 +4274,22 @@
         <v>94</v>
       </c>
       <c r="B96" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="C96" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="C96" s="15" t="s">
+      <c r="D96" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="D96" s="15" t="s">
+      <c r="E96" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="F96" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="G96" s="17" t="s">
         <v>229</v>
-      </c>
-      <c r="E96" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F96" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="G96" s="17" t="s">
-        <v>230</v>
       </c>
       <c r="H96" s="17"/>
     </row>
@@ -4242,19 +4298,19 @@
         <v>95</v>
       </c>
       <c r="B97" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F97" s="9" t="s">
         <v>193</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D97" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="E97" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F97" s="9" t="s">
-        <v>194</v>
       </c>
       <c r="G97" s="10" t="s">
         <v>2</v>
@@ -4266,19 +4322,19 @@
         <v>96</v>
       </c>
       <c r="B98" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F98" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D98" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F98" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="G98" s="10" t="s">
         <v>2</v>
@@ -4290,7 +4346,7 @@
         <v>97</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>0</v>
@@ -4302,7 +4358,7 @@
         <v>2</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G99" s="10" t="s">
         <v>2</v>
@@ -4314,7 +4370,7 @@
         <v>98</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>0</v>
@@ -4326,7 +4382,7 @@
         <v>2</v>
       </c>
       <c r="F100" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G100" s="10" t="s">
         <v>2</v>
@@ -4341,19 +4397,19 @@
         <v>5</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F101" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G101" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H101" s="14"/>
     </row>
@@ -4365,19 +4421,19 @@
         <v>6</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F102" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G102" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H102" s="14"/>
     </row>

--- a/STM32H743VIT6引脚定义.xlsx
+++ b/STM32H743VIT6引脚定义.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MCU_Project\STM32H743Project\02High_Speed_Collection_AD7616\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B2C65A-8F40-459A-8B8E-C073A17B4C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFC2600-61ED-4C58-BB97-4386565F6DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D862D2F7-4BB5-4946-9DE3-EE852D9A2767}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="273">
   <si>
     <t>I/O</t>
   </si>
@@ -1336,6 +1336,10 @@
   </si>
   <si>
     <t>USB_OTG_HS_ULPI_STP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PB12</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3209,8 +3213,8 @@
       <c r="A53" s="7">
         <v>51</v>
       </c>
-      <c r="B53" s="8">
-        <v>5</v>
+      <c r="B53" s="8" t="s">
+        <v>272</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>0</v>

--- a/STM32H743VIT6引脚定义.xlsx
+++ b/STM32H743VIT6引脚定义.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MCU_Project\STM32H743Project\02High_Speed_Collection_AD7616\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFC2600-61ED-4C58-BB97-4386565F6DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A690A9E-6780-43F7-913D-26841EC60354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D862D2F7-4BB5-4946-9DE3-EE852D9A2767}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="276">
   <si>
     <t>I/O</t>
   </si>
@@ -1340,6 +1340,18 @@
   </si>
   <si>
     <t>PB12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AD7616_CONVST</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AD7616_BUSY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Light_Pulse</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2529,7 +2541,9 @@
       <c r="G25" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H25" s="10"/>
+      <c r="H25" s="10" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
@@ -2701,7 +2715,9 @@
       <c r="G32" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="H32" s="10"/>
+      <c r="H32" s="10" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="33" spans="1:8" ht="60" x14ac:dyDescent="0.2">
       <c r="A33" s="7">
@@ -4367,7 +4383,9 @@
       <c r="G99" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="H99" s="10"/>
+      <c r="H99" s="10" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="100" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A100" s="7">
